--- a/Team 1.xlsx
+++ b/Team 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Виктор\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ВикторАДиндев\Desktop\delete\11-team-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE6352F7-5DA9-4387-B900-2F8197F55A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A760983-5A2B-45A3-BE80-39225829B006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B865B7AF-A1AD-49C3-BCF6-1A6CF120E971}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B865B7AF-A1AD-49C3-BCF6-1A6CF120E971}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -283,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -326,22 +326,23 @@
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Нормален" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -357,9 +358,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема на Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Оffice">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -397,7 +398,7 @@
         <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Оffice">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
@@ -503,7 +504,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Оffice">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -673,66 +674,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{733E4029-6CC0-48F4-9A54-B451B5EF9BD2}">
-  <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="22.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="19"/>
+      <c r="B2" s="19"/>
       <c r="D2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="20"/>
-      <c r="F2" s="19"/>
+      <c r="E2" s="19"/>
       <c r="G2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="20"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="19"/>
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="19"/>
       <c r="G3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="19"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="1"/>
@@ -741,9 +726,8 @@
       <c r="F4" s="1"/>
       <c r="G4" s="4"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="19"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
       <c r="C5" s="1"/>
@@ -752,9 +736,8 @@
       <c r="F5" s="1"/>
       <c r="G5" s="6"/>
       <c r="H5" s="7"/>
-      <c r="I5" s="19"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="1"/>
@@ -763,9 +746,8 @@
       <c r="F6" s="1"/>
       <c r="G6" s="6"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="6"/>
       <c r="B7" s="7"/>
       <c r="C7" s="1"/>
@@ -774,9 +756,8 @@
       <c r="F7" s="1"/>
       <c r="G7" s="6"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="19"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="6"/>
       <c r="B8" s="7"/>
       <c r="C8" s="1"/>
@@ -785,9 +766,8 @@
       <c r="F8" s="1"/>
       <c r="G8" s="6"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="8"/>
       <c r="B9" s="9"/>
       <c r="C9" s="1"/>
@@ -796,32 +776,28 @@
       <c r="F9" s="1"/>
       <c r="G9" s="8"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="19"/>
-    </row>
-    <row r="10" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="19"/>
       <c r="D10" s="15" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="19"/>
       <c r="G10" s="15" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="1"/>
@@ -830,9 +806,8 @@
       <c r="F11" s="1"/>
       <c r="G11" s="4"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="19"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="1"/>
@@ -841,9 +816,8 @@
       <c r="F12" s="1"/>
       <c r="G12" s="6"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="1"/>
@@ -852,9 +826,8 @@
       <c r="F13" s="1"/>
       <c r="G13" s="6"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="19"/>
-    </row>
-    <row r="14" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="1"/>
@@ -863,49 +836,42 @@
       <c r="F14" s="1"/>
       <c r="G14" s="8"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="19"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="17" t="s">
         <v>5</v>
       </c>
       <c r="B15" s="18"/>
-      <c r="C15" s="19"/>
       <c r="D15" s="17" t="s">
         <v>5</v>
       </c>
       <c r="E15" s="18"/>
-      <c r="F15" s="19"/>
       <c r="G15" s="17" t="s">
         <v>5</v>
       </c>
       <c r="H15" s="18"/>
-      <c r="I15" s="19"/>
-    </row>
-    <row r="16" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="13" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="19"/>
       <c r="D16" s="13" t="s">
         <v>6</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="19"/>
       <c r="G16" s="13" t="s">
         <v>6</v>
       </c>
       <c r="H16" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I16" s="19"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="1"/>
@@ -914,9 +880,8 @@
       <c r="F17" s="1"/>
       <c r="G17" s="4"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="19"/>
-    </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="1"/>
@@ -925,9 +890,8 @@
       <c r="F18" s="1"/>
       <c r="G18" s="6"/>
       <c r="H18" s="7"/>
-      <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="1"/>
@@ -936,9 +900,8 @@
       <c r="F19" s="1"/>
       <c r="G19" s="6"/>
       <c r="H19" s="7"/>
-      <c r="I19" s="19"/>
-    </row>
-    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="1"/>
@@ -947,9 +910,8 @@
       <c r="F20" s="1"/>
       <c r="G20" s="6"/>
       <c r="H20" s="7"/>
-      <c r="I20" s="19"/>
-    </row>
-    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="1"/>
@@ -958,9 +920,8 @@
       <c r="F21" s="1"/>
       <c r="G21" s="6"/>
       <c r="H21" s="7"/>
-      <c r="I21" s="19"/>
-    </row>
-    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
       <c r="C22" s="1"/>
@@ -969,9 +930,8 @@
       <c r="F22" s="1"/>
       <c r="G22" s="6"/>
       <c r="H22" s="7"/>
-      <c r="I22" s="19"/>
-    </row>
-    <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="1"/>
@@ -980,9 +940,8 @@
       <c r="F23" s="1"/>
       <c r="G23" s="6"/>
       <c r="H23" s="7"/>
-      <c r="I23" s="19"/>
-    </row>
-    <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.4">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
       <c r="C24" s="1"/>
@@ -991,9 +950,8 @@
       <c r="F24" s="1"/>
       <c r="G24" s="6"/>
       <c r="H24" s="7"/>
-      <c r="I24" s="19"/>
-    </row>
-    <row r="25" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="1"/>
@@ -1002,43 +960,8 @@
       <c r="F25" s="1"/>
       <c r="G25" s="10"/>
       <c r="H25" s="11"/>
-      <c r="I25" s="19"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="e/6LJjD8h08eofQC5/fP684i8r/YX0ZwV6u7aVXRjHa77tGTXEDImB6jWveN9FeqeqUnmF9HWewbDRcZfEHeuw==" saltValue="u116h3sE+C4fdPdLUorFzQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="3">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="D15:E15"/>
